--- a/106/food/kp2026.xlsx
+++ b/106/food/kp2026.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF13"/>
+  <dimension ref="A1:AF23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.85546875" customWidth="1" style="11" min="1" max="1"/>
@@ -1443,6 +1443,13 @@
       </c>
       <c r="AF13" s="4" t="n"/>
     </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="AD1:AE1"/>
